--- a/Excel/FashionSpecialConfig.xlsx
+++ b/Excel/FashionSpecialConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="28">
   <si>
     <t>#</t>
   </si>
@@ -93,6 +93,24 @@
   </si>
   <si>
     <t>小女道士</t>
+  </si>
+  <si>
+    <t>男战士</t>
+  </si>
+  <si>
+    <t>女战士</t>
+  </si>
+  <si>
+    <t>男法师</t>
+  </si>
+  <si>
+    <t>女法师</t>
+  </si>
+  <si>
+    <t>男道士</t>
+  </si>
+  <si>
+    <t>女道士</t>
   </si>
 </sst>
 </file>
@@ -1052,18 +1070,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1238938053097" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.6371681415929" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.0442477876106" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.8053097345133" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.2477876106195" style="1" customWidth="1"/>
-    <col min="9" max="10" width="12.8141592920354" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6333333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.0416666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.8083333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.25" style="1" customWidth="1"/>
+    <col min="9" max="10" width="12.8166666666667" style="2" customWidth="1"/>
     <col min="11" max="16368" width="9" style="2"/>
     <col min="16369" max="16384" width="9" style="1"/>
   </cols>
@@ -1330,9 +1348,165 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12" customHeight="1" spans="3:10">
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="1">
+        <v>2004</v>
+      </c>
+      <c r="I12" s="1">
+        <v>50</v>
+      </c>
+      <c r="J12" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:10">
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2004</v>
+      </c>
+      <c r="I13" s="1">
+        <v>50</v>
+      </c>
+      <c r="J13" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:10">
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="1">
+        <v>2005</v>
+      </c>
+      <c r="I14" s="1">
+        <v>50</v>
+      </c>
+      <c r="J14" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:10">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2005</v>
+      </c>
+      <c r="I15" s="1">
+        <v>50</v>
+      </c>
+      <c r="J15" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:10">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="1">
+        <v>2006</v>
+      </c>
+      <c r="I16" s="1">
+        <v>50</v>
+      </c>
+      <c r="J16" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:10">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2006</v>
+      </c>
+      <c r="I17" s="1">
+        <v>50</v>
+      </c>
+      <c r="J17" s="1">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:I3 J3 H4 J4 J5 I4:I5 C3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:J3 H4 C3:G5 I4:J5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/FashionSpecialConfig.xlsx
+++ b/Excel/FashionSpecialConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="29">
   <si>
     <t>#</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>男战士</t>
+  </si>
+  <si>
+    <t>150,300,450,150</t>
   </si>
   <si>
     <t>女战士</t>
@@ -1359,19 +1362,19 @@
         <v>14</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="1">
-        <v>2004</v>
+        <v>31</v>
       </c>
       <c r="I12" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J12" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:10">
@@ -1379,25 +1382,25 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="1">
-        <v>2004</v>
+        <v>32</v>
       </c>
       <c r="I13" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="J13" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:10">
@@ -1405,25 +1408,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>16</v>
       </c>
       <c r="H14" s="1">
-        <v>2005</v>
+        <v>31</v>
       </c>
       <c r="I14" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J14" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:10">
@@ -1431,25 +1434,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>16</v>
       </c>
       <c r="H15" s="1">
-        <v>2005</v>
+        <v>32</v>
       </c>
       <c r="I15" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="J15" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:10">
@@ -1457,25 +1460,25 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="H16" s="1">
-        <v>2006</v>
+        <v>31</v>
       </c>
       <c r="I16" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J16" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:10">
@@ -1483,25 +1486,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>16</v>
       </c>
       <c r="H17" s="1">
-        <v>2006</v>
+        <v>32</v>
       </c>
       <c r="I17" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="J17" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/FashionSpecialConfig.xlsx
+++ b/Excel/FashionSpecialConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="32">
   <si>
     <t>#</t>
   </si>
@@ -98,10 +98,19 @@
     <t>男战士</t>
   </si>
   <si>
-    <t>150,300,450,150</t>
+    <t>2001,2002,2003,31</t>
+  </si>
+  <si>
+    <t>150,300,450,6</t>
   </si>
   <si>
     <t>女战士</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,32</t>
+  </si>
+  <si>
+    <t>150,300,450,3</t>
   </si>
   <si>
     <t>男法师</t>
@@ -1359,10 +1368,10 @@
         <v>22</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>16</v>
@@ -1382,13 +1391,13 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>16</v>
@@ -1408,13 +1417,13 @@
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>16</v>
@@ -1434,13 +1443,13 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>14</v>
-      </c>
       <c r="F15" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>16</v>
@@ -1460,13 +1469,13 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>16</v>
@@ -1486,13 +1495,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>16</v>

--- a/Excel/FashionSpecialConfig.xlsx
+++ b/Excel/FashionSpecialConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="41">
   <si>
     <t>#</t>
   </si>
@@ -123,6 +123,33 @@
   </si>
   <si>
     <t>女道士</t>
+  </si>
+  <si>
+    <t>经验多多</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,50</t>
+  </si>
+  <si>
+    <t>200,400,600,10</t>
+  </si>
+  <si>
+    <t>金币多多</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,51</t>
+  </si>
+  <si>
+    <t>爆率多多</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,52</t>
+  </si>
+  <si>
+    <t>品质高高</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,53</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1109,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1516,6 +1543,110 @@
         <v>20</v>
       </c>
     </row>
+    <row r="18" customHeight="1" spans="3:10">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1">
+        <v>50</v>
+      </c>
+      <c r="I18" s="1">
+        <v>15</v>
+      </c>
+      <c r="J18" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:10">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="1">
+        <v>51</v>
+      </c>
+      <c r="I19" s="1">
+        <v>15</v>
+      </c>
+      <c r="J19" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:10">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="1">
+        <v>52</v>
+      </c>
+      <c r="I20" s="1">
+        <v>15</v>
+      </c>
+      <c r="J20" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:10">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="1">
+        <v>53</v>
+      </c>
+      <c r="I21" s="1">
+        <v>15</v>
+      </c>
+      <c r="J21" s="1">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:J3 H4 C3:G5 I4:J5" errorStyle="warning">

--- a/Excel/FashionSpecialConfig.xlsx
+++ b/Excel/FashionSpecialConfig.xlsx
@@ -1563,7 +1563,7 @@
         <v>50</v>
       </c>
       <c r="I18" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J18" s="1">
         <v>30</v>
@@ -1589,7 +1589,7 @@
         <v>51</v>
       </c>
       <c r="I19" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J19" s="1">
         <v>30</v>
@@ -1615,7 +1615,7 @@
         <v>52</v>
       </c>
       <c r="I20" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J20" s="1">
         <v>30</v>
@@ -1641,7 +1641,7 @@
         <v>53</v>
       </c>
       <c r="I21" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J21" s="1">
         <v>30</v>

--- a/Excel/FashionSpecialConfig.xlsx
+++ b/Excel/FashionSpecialConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
   <si>
     <t>#</t>
   </si>
@@ -150,6 +150,24 @@
   </si>
   <si>
     <t>2001,2002,2003,53</t>
+  </si>
+  <si>
+    <t>刀</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2013</t>
+  </si>
+  <si>
+    <t>200,400,600,300</t>
+  </si>
+  <si>
+    <t>枪</t>
+  </si>
+  <si>
+    <t>剑</t>
+  </si>
+  <si>
+    <t>戟</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1127,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1647,6 +1665,142 @@
         <v>30</v>
       </c>
     </row>
+    <row r="22" customHeight="1" spans="3:10">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="1">
+        <v>2013</v>
+      </c>
+      <c r="I22" s="1">
+        <v>200</v>
+      </c>
+      <c r="J22" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:10">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="1">
+        <v>2013</v>
+      </c>
+      <c r="I23" s="1">
+        <v>200</v>
+      </c>
+      <c r="J23" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:10">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="1">
+        <v>2013</v>
+      </c>
+      <c r="I24" s="1">
+        <v>200</v>
+      </c>
+      <c r="J24" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:10">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="1">
+        <v>2013</v>
+      </c>
+      <c r="I25" s="1">
+        <v>200</v>
+      </c>
+      <c r="J25" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="5:10">
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" customHeight="1" spans="5:10">
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" customHeight="1" spans="5:10">
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" customHeight="1" spans="5:10">
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:J3 H4 C3:G5 I4:J5" errorStyle="warning">

--- a/Excel/FashionSpecialConfig.xlsx
+++ b/Excel/FashionSpecialConfig.xlsx
@@ -158,7 +158,7 @@
     <t>2001,2002,2003,2013</t>
   </si>
   <si>
-    <t>200,400,600,300</t>
+    <t>200,400,600,400</t>
   </si>
   <si>
     <t>枪</t>
@@ -1773,7 +1773,6 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
@@ -1781,7 +1780,6 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
     </row>
@@ -1789,7 +1787,6 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
     </row>
@@ -1797,7 +1794,6 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>

--- a/Excel/FashionSpecialConfig.xlsx
+++ b/Excel/FashionSpecialConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="57">
   <si>
     <t>#</t>
   </si>
@@ -168,6 +168,36 @@
   </si>
   <si>
     <t>戟</t>
+  </si>
+  <si>
+    <t>神攻</t>
+  </si>
+  <si>
+    <t>2001,2003,2013,91</t>
+  </si>
+  <si>
+    <t>200,600,300,10</t>
+  </si>
+  <si>
+    <t>神血</t>
+  </si>
+  <si>
+    <t>2001,2003,2013,92</t>
+  </si>
+  <si>
+    <t>神防</t>
+  </si>
+  <si>
+    <t>2001,2003,2013,93</t>
+  </si>
+  <si>
+    <t>神攻防血</t>
+  </si>
+  <si>
+    <t>2001,2003,2013,94</t>
+  </si>
+  <si>
+    <t>200,600,300,6</t>
   </si>
 </sst>
 </file>
@@ -1249,7 +1279,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1275,7 +1305,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1301,7 +1331,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1327,7 +1357,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1353,7 +1383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1379,7 +1409,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1405,7 +1435,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:10">
+    <row r="12" customHeight="1" spans="1:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1431,7 +1461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:10">
+    <row r="13" customHeight="1" spans="1:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1457,7 +1487,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:10">
+    <row r="14" customHeight="1" spans="1:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1483,7 +1513,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:10">
+    <row r="15" customHeight="1" spans="1:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1509,7 +1539,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:10">
+    <row r="16" customHeight="1" spans="1:10">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1769,37 +1799,113 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="5:10">
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" customHeight="1" spans="5:10">
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="5:10">
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" customHeight="1" spans="5:10">
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
+    <row r="26" customHeight="1" spans="3:10">
+      <c r="C26" s="1">
+        <v>21</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="1">
+        <v>91</v>
+      </c>
+      <c r="I26" s="1">
+        <v>5</v>
+      </c>
+      <c r="J26" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:10">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="1">
+        <v>92</v>
+      </c>
+      <c r="I27" s="1">
+        <v>5</v>
+      </c>
+      <c r="J27" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:10">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="1">
+        <v>93</v>
+      </c>
+      <c r="I28" s="1">
+        <v>5</v>
+      </c>
+      <c r="J28" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:10">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="1">
+        <v>94</v>
+      </c>
+      <c r="I29" s="1">
+        <v>3</v>
+      </c>
+      <c r="J29" s="1">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:J3 H4 C3:G5 I4:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:G5 I5:J5 C3:J4" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/FashionSpecialConfig.xlsx
+++ b/Excel/FashionSpecialConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="62">
   <si>
     <t>#</t>
   </si>
@@ -198,6 +198,21 @@
   </si>
   <si>
     <t>200,600,300,6</t>
+  </si>
+  <si>
+    <t>2001,2003,2007,91</t>
+  </si>
+  <si>
+    <t>2001,2003,2008,92</t>
+  </si>
+  <si>
+    <t>2001,2003,2009,93</t>
+  </si>
+  <si>
+    <t>2001,2003,2010,94</t>
+  </si>
+  <si>
+    <t>200,600,200,6</t>
   </si>
 </sst>
 </file>
@@ -1157,7 +1172,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1903,6 +1918,110 @@
         <v>30</v>
       </c>
     </row>
+    <row r="30" customHeight="1" spans="3:10">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="1">
+        <v>91</v>
+      </c>
+      <c r="I30" s="1">
+        <v>5</v>
+      </c>
+      <c r="J30" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:10">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="1">
+        <v>92</v>
+      </c>
+      <c r="I31" s="1">
+        <v>5</v>
+      </c>
+      <c r="J31" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:10">
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="1">
+        <v>93</v>
+      </c>
+      <c r="I32" s="1">
+        <v>5</v>
+      </c>
+      <c r="J32" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:10">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="1">
+        <v>94</v>
+      </c>
+      <c r="I33" s="1">
+        <v>3</v>
+      </c>
+      <c r="J33" s="1">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:G5 I5:J5 C3:J4" errorStyle="warning">

--- a/Excel/FashionSpecialConfig.xlsx
+++ b/Excel/FashionSpecialConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="63">
   <si>
     <t>#</t>
   </si>
@@ -203,6 +203,9 @@
     <t>2001,2003,2007,91</t>
   </si>
   <si>
+    <t>200,600,200,10</t>
+  </si>
+  <si>
     <t>2001,2003,2008,92</t>
   </si>
   <si>
@@ -212,7 +215,7 @@
     <t>2001,2003,2010,94</t>
   </si>
   <si>
-    <t>200,600,200,6</t>
+    <t>200,600,100,6</t>
   </si>
 </sst>
 </file>
@@ -1929,7 +1932,7 @@
         <v>57</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>16</v>
@@ -1952,10 +1955,10 @@
         <v>50</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>16</v>
@@ -1978,10 +1981,10 @@
         <v>52</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>16</v>
@@ -2004,10 +2007,10 @@
         <v>54</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>16</v>

--- a/Excel/FashionSpecialConfig.xlsx
+++ b/Excel/FashionSpecialConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="63">
   <si>
     <t>#</t>
   </si>
@@ -1175,7 +1175,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2025,6 +2025,110 @@
         <v>30</v>
       </c>
     </row>
+    <row r="34" customHeight="1" spans="3:10">
+      <c r="C34" s="1">
+        <v>29</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="1">
+        <v>91</v>
+      </c>
+      <c r="I34" s="1">
+        <v>5</v>
+      </c>
+      <c r="J34" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:10">
+      <c r="C35" s="1">
+        <v>30</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="1">
+        <v>92</v>
+      </c>
+      <c r="I35" s="1">
+        <v>5</v>
+      </c>
+      <c r="J35" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:10">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="1">
+        <v>93</v>
+      </c>
+      <c r="I36" s="1">
+        <v>5</v>
+      </c>
+      <c r="J36" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:10">
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="1">
+        <v>94</v>
+      </c>
+      <c r="I37" s="1">
+        <v>3</v>
+      </c>
+      <c r="J37" s="1">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:G5 I5:J5 C3:J4" errorStyle="warning">

--- a/Excel/FashionSpecialConfig.xlsx
+++ b/Excel/FashionSpecialConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="63">
   <si>
     <t>#</t>
   </si>
@@ -1175,7 +1175,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2129,6 +2129,110 @@
         <v>30</v>
       </c>
     </row>
+    <row r="38" customHeight="1" spans="3:10">
+      <c r="C38" s="1">
+        <v>33</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="1">
+        <v>91</v>
+      </c>
+      <c r="I38" s="1">
+        <v>5</v>
+      </c>
+      <c r="J38" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:10">
+      <c r="C39" s="1">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="1">
+        <v>92</v>
+      </c>
+      <c r="I39" s="1">
+        <v>5</v>
+      </c>
+      <c r="J39" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:10">
+      <c r="C40" s="1">
+        <v>35</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="1">
+        <v>93</v>
+      </c>
+      <c r="I40" s="1">
+        <v>5</v>
+      </c>
+      <c r="J40" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:10">
+      <c r="C41" s="1">
+        <v>36</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="1">
+        <v>94</v>
+      </c>
+      <c r="I41" s="1">
+        <v>3</v>
+      </c>
+      <c r="J41" s="1">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:G5 I5:J5 C3:J4" errorStyle="warning">

--- a/Excel/FashionSpecialConfig.xlsx
+++ b/Excel/FashionSpecialConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="63">
   <si>
     <t>#</t>
   </si>
@@ -1175,7 +1180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2233,6 +2238,110 @@
         <v>30</v>
       </c>
     </row>
+    <row r="42" customHeight="1" spans="3:10">
+      <c r="C42" s="1">
+        <v>37</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="1">
+        <v>91</v>
+      </c>
+      <c r="I42" s="1">
+        <v>5</v>
+      </c>
+      <c r="J42" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:10">
+      <c r="C43" s="1">
+        <v>38</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="1">
+        <v>92</v>
+      </c>
+      <c r="I43" s="1">
+        <v>5</v>
+      </c>
+      <c r="J43" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:10">
+      <c r="C44" s="1">
+        <v>39</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="1">
+        <v>93</v>
+      </c>
+      <c r="I44" s="1">
+        <v>5</v>
+      </c>
+      <c r="J44" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:10">
+      <c r="C45" s="1">
+        <v>40</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="1">
+        <v>94</v>
+      </c>
+      <c r="I45" s="1">
+        <v>3</v>
+      </c>
+      <c r="J45" s="1">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:G5 I5:J5 C3:J4" errorStyle="warning">
